--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -2866,7 +2866,7 @@
   </sheetData>
   <dataValidations count="5">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography"</formula1>
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
@@ -3240,13 +3240,13 @@
   </sheetData>
   <dataValidations count="3">
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography"</formula1>
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"x_ray_diffraction,neutron_diffraction,electron_diffraction,fiber_diffraction"</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"raw,preprocessing,processing,completed,failed"</formula1>
+      <formula1>"collected,raw,preprocessing,processing,completed,failed"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -2753,7 +2753,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2804,80 +2804,104 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>lims_system</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>daq_system</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>control_system</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>instrument_code</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>instrument_category</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>facility_ror</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="5">
+  <dataValidations count="8">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
     </dataValidation>
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ispyb,ispyb_diamond,icat,mxlive,mxcube,user_office"</formula1>
+    </dataValidation>
     <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"bluesky,spec,sardana,gda,mxcube,blu_ice,jblue_ice"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"epics,tango,labview,opi"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2942,7 +2966,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BF1"/>
+  <dimension ref="A1:BG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2998,247 +3022,252 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>daq_system</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
           <t>magnification</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>calibrated_pixel_size</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>camera_binning</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>exposure_time_per_frame</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>frames_per_movie</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>total_exposure_time</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>total_dose</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>dose_rate</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>defocus_target</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>defocus_range_min</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>defocus_range_max</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>defocus_range_increment</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>astigmatism_target</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>coma</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>stage_tilt</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>autoloader_slot</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>shots_per_hole</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>holes_per_group</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>acquisition_software</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>acquisition_software_version</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>wavelength</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>oscillation_angle</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>start_angle</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>number_of_images</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>beam_center_x</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>beam_center_y</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>detector_distance</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>pixel_size_x</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>pixel_size_y</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>total_rotation</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>beamline</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>transmission</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>flux</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>flux_end</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>slit_gap_horizontal</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>slit_gap_vertical</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>undulator_gap</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>synchrotron_mode</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>exposure_time</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>start_time</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>end_time</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>resolution</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>resolution_at_corner</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>ispyb_data_collection_id</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>ispyb_session_id</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
     </dataValidation>
@@ -3247,6 +3276,9 @@
     </dataValidation>
     <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"collected,raw,preprocessing,processing,completed,failed"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"bluesky,spec,sardana,gda,mxcube,blu_ice,jblue_ice"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -1596,7 +1596,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1752,15 +1752,20 @@
       </c>
       <c r="AE1" t="inlineStr">
         <is>
+          <t>oligomeric_state</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3725,7 +3730,7 @@
   </sheetData>
   <dataValidations count="2">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"mrc,tiff,hdf5,star,pdb,mmcif,mtz,cbf,cbf_zst,img,h5,ascii,thermo_raw,zip,mrcs,eer,cs,json,csv,ccp4,gz"</formula1>
+      <formula1>"mrc,tiff,hdf5,star,pdb,mmcif,mtz,cbf,cbf_zst,img,h5,ascii,thermo_raw,zip,tar,mrcs,eer,cs,json,csv,ccp4,gz"</formula1>
     </dataValidation>
     <dataValidation sqref="G2:G1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"micrograph,diffraction,scattering,particles,volume,model,metadata,raw_data,processed_data,movie,motion_corrected,ctf_estimation,particle_coordinates,class_averages,fsc_curve,map_half,validation_report"</formula1>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -34,46 +34,50 @@
     <sheet name="Instrument" sheetId="25" state="visible" r:id="rId25"/>
     <sheet name="CryoEMInstrument" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="XRayInstrument" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="SAXSInstrument" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="BeamlineInstrument" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="ExperimentRun" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="WorkflowRun" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="DataFile" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="Image" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="Image2D" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="Image3D" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="Movie" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Micrograph" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="FTIRImage" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="FluorescenceImage" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="OpticalImage" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="XRFImage" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="ImageFeature" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="OntologyTerm" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="MolecularComposition" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="BufferComposition" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="StorageConditions" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="CryoEMPreparation" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="CrystallizationConditions" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="XRayPreparation" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="SAXSPreparation" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="ExperimentalConditions" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="DataCollectionStrategy" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="QualityMetrics" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="ComputeResources" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="MotionCorrectionParameters" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="CTFEstimationParameters" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="ParticlePickingParameters" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="RefinementParameters" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="FSCCurve" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="StudySampleAssociation" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="StudyExperimentAssociation" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="StudyWorkflowAssociation" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="ExperimentSampleAssociation" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="ExperimentInstrumentAssociation" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="WorkflowExperimentAssociation" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="WorkflowInputAssociation" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="WorkflowOutputAssociation" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="SANSDetector" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="SANSSource" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="SANSConfiguration" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="SANSInstrument" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="SAXSInstrument" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="BeamlineInstrument" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="ExperimentRun" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="WorkflowRun" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="DataFile" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="Image" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="Image2D" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Image3D" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Movie" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Micrograph" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="FTIRImage" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="FluorescenceImage" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="OpticalImage" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="XRFImage" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="ImageFeature" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="OntologyTerm" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="MolecularComposition" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="BufferComposition" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="StorageConditions" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="CryoEMPreparation" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="CrystallizationConditions" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="XRayPreparation" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="SAXSPreparation" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="ExperimentalConditions" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="DataCollectionStrategy" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="QualityMetrics" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="ComputeResources" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="MotionCorrectionParameters" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="CTFEstimationParameters" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="ParticlePickingParameters" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="RefinementParameters" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="FSCCurve" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="StudySampleAssociation" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="StudyExperimentAssociation" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="StudyWorkflowAssociation" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="ExperimentSampleAssociation" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="ExperimentInstrumentAssociation" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="WorkflowExperimentAssociation" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="WorkflowInputAssociation" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="WorkflowOutputAssociation" sheetId="71" state="visible" r:id="rId71"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2641,113 +2645,67 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:K1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>q_range_min</t>
+          <t>detector_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>q_range_max</t>
+          <t>detector_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>detector_distance_min</t>
+          <t>detector_description</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>detector_distance_max</t>
+          <t>pixel_size_x</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>sample_changer_capacity</t>
+          <t>pixel_size_y</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>temperature_control_range</t>
+          <t>sample_detector_distance</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>instrument_code</t>
+          <t>rotation_angle</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>instrument_category</t>
+          <t>beam_trap_type</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>facility_name</t>
+          <t>beam_trap_position_x</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>facility_ror</t>
+          <t>beam_trap_position_y</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
-        <is>
-          <t>beamline_id</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"operational,maintenance,offline,commissioning"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2758,158 +2716,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>techniques_supported</t>
+          <t>source_type</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>source_type</t>
+          <t>source_description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>energy_min</t>
+          <t>wavelength</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>energy_max</t>
+          <t>wavelength_spread</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>q_range_min</t>
+          <t>wavelength_selection_method</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>q_range_max</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>sample_changer_capacity</t>
+          <t>flux</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
-        <is>
-          <t>mail_in_service</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>website</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>lims_system</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>daq_system</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>control_system</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>instrument_code</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>instrument_category</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>facility_name</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>facility_ror</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>beamline_id</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>manufacturer</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>model</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>installation_date</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>current_status</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="8">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
-    </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"ispyb,ispyb_diamond,icat,mxlive,mxcube_lims,user_office"</formula1>
-    </dataValidation>
-    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"bluesky,spec,sardana,gda,mxcube_daq,blu_ice,jblue_ice"</formula1>
-    </dataValidation>
-    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"epics,tango,labview,opi"</formula1>
-    </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
-    </dataValidation>
-    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"operational,maintenance,offline,commissioning"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2971,6 +2823,491 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>q_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>number_of_guides</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attenuator</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_aperature_diameter</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sample_aperature_diameter</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>siwindow_to_main_distance</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sample_ap_to_si_distance</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sample_ap_to_main_distance</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sample_ap_to_sample_distance</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source_ap_to_siwindow_distance</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source_ap_to_sample_ap_distance</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>technique</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_range_min</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>q_range_max</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>detectors</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>configuration</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>environment</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>instrument_code</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>instrument_category</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>facility_name</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>facility_ror</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>beamline_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>installation_date</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>q_range_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_range_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>detector_distance_min</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>detector_distance_max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>sample_changer_capacity</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>temperature_control_range</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>instrument_code</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>instrument_category</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>facility_name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>facility_ror</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>beamline_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>installation_date</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:X1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>techniques_supported</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>energy_min</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>energy_max</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>q_range_min</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>q_range_max</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sample_changer_capacity</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>mail_in_service</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>lims_system</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>daq_system</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>control_system</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>instrument_code</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>instrument_category</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>facility_name</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>facility_ror</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>beamline_id</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>installation_date</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>current_status</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="8">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ispyb,ispyb_diamond,icat,mxlive,mxcube_lims,user_office"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"bluesky,spec,sardana,gda,mxcube_daq,blu_ice,jblue_ice"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"epics,tango,labview,opi"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"operational,maintenance,offline,commissioning"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:BG1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -3290,7 +3627,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3651,7 +3988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3740,7 +4077,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3806,7 +4143,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3882,7 +4219,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3953,485 +4290,6 @@
         </is>
       </c>
       <c r="M1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>frames</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>super_resolution</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>pixel_size_unbinned</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>stage_position_x</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>stage_position_y</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>stage_position_z</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>nominal_defocus</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>dose_per_frame</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>beam_shift_x</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>beam_shift_y</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ice_thickness_estimate</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>grid_square_id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>hole_id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>acquisition_group</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>origin_movie_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>defocus_u</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>defocus_v</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>astigmatism_angle</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>resolution_fit_limit</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ctf_quality_score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>wavenumber_min</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>wavenumber_max</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>spectral_resolution</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>number_of_scans</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>apodization_function</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>molecular_signatures</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>background_correction</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>excitation_wavelength</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>emission_wavelength</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>excitation_filter</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>emission_filter</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>fluorophore</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>channel_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>laser_power</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pinhole_size</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>quantum_yield</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -4484,83 +4342,234 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>frames</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>super_resolution</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pixel_size_unbinned</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stage_position_x</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>stage_position_y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stage_position_z</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>nominal_defocus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dose_per_frame</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>beam_shift_x</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>beam_shift_y</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ice_thickness_estimate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>grid_square_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>hole_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>acquisition_group</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>illumination_type</t>
+          <t>dose</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>magnification</t>
+          <t>origin_movie_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>numerical_aperture</t>
+          <t>defocus_u</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>color_channels</t>
+          <t>defocus_v</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>white_balance</t>
+          <t>astigmatism_angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>contrast_method</t>
+          <t>resolution_fit_limit</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>ctf_quality_score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>defocus</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>astigmatism</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>file_name</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>acquisition_date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>pixel_size</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>dimensions_x</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>dimensions_y</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>dose</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
@@ -4580,16 +4589,112 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"brightfield,darkfield,phase_contrast,dic,fluorescence,confocal,polarized,oblique"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>wavenumber_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>wavenumber_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spectral_resolution</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>number_of_scans</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>apodization_function</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>molecular_signatures</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>background_correction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4601,6 +4706,238 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>excitation_wavelength</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>emission_wavelength</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>excitation_filter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>emission_filter</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fluorophore</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>channel_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>laser_power</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pinhole_size</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>quantum_yield</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>illumination_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>magnification</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>numerical_aperture</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>color_channels</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>white_balance</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>contrast_method</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"brightfield,darkfield,phase_contrast,dic,fluorescence,confocal,polarized,oblique"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>beam_energy</t>
         </is>
       </c>
@@ -4718,7 +5055,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4744,7 +5081,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4795,7 +5132,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4831,7 +5168,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4863,426 +5200,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>atmosphere</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:W1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>grid_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>support_film</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>hole_size</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>vitrification_method</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>blot_time</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>blot_force</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>humidity_percentage</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>chamber_temperature</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>grid_material</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>glow_discharge_applied</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>glow_discharge_time</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>glow_discharge_current</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>glow_discharge_atmosphere</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>glow_discharge_pressure</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>vitrification_instrument</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>blot_number</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>wait_time</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>blotter_height</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>blotter_setting</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>sample_applied_volume</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>ethane_temperature</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>plasma_treatment</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="3">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"c_flat,quantifoil,lacey_carbon,ultrathin_carbon,gold"</formula1>
-    </dataValidation>
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"plunge_freezing,high_pressure_freezing,slam_freezing"</formula1>
-    </dataValidation>
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"carbon,gold,graphene,silicon_nitride"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:N1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>method</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>crystallization_conditions</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>drop_volume</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>protein_concentration</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>crystal_size_um</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>cryo_protectant</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>crystal_id</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>screen_name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>temperature_c</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>drop_ratio_protein_to_reservoir</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>reservoir_volume_ul</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>seeding_type</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>seed_stock_dilution</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"vapor_diffusion_hanging,vapor_diffusion_sitting,batch,microbatch,lcp,dialysis,free_interface_diffusion"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Z1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>protein_concentration_mg_per_ml</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>protein_buffer</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>additives</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>crystallization_method</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>crystallization_conditions</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>screen_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>temperature_c</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>drop_ratio_protein_to_reservoir</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>drop_volume_nl</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>reservoir_volume_ul</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>seeding_type</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>seed_stock_dilution</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>initial_hit_condition</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>optimization_strategy</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>optimized_condition</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>crystal_size_um</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>cryoprotectant</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>cryoprotectant_concentration</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>soak_compound</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>soak_conditions</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>mounting_method</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>flash_cooling_method</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>crystal_notes</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>loop_size</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>mounting_temperature</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"vapor_diffusion_hanging,vapor_diffusion_sitting,batch,microbatch,lcp,dialysis,free_interface_diffusion"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5324,6 +5241,426 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>duration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>atmosphere</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:W1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>grid_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>support_film</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>hole_size</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>vitrification_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>blot_time</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>blot_force</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>humidity_percentage</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>chamber_temperature</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>grid_material</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>glow_discharge_applied</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>glow_discharge_time</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>glow_discharge_current</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>glow_discharge_atmosphere</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>glow_discharge_pressure</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>vitrification_instrument</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>blot_number</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>wait_time</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>blotter_height</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>blotter_setting</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sample_applied_volume</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>ethane_temperature</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>plasma_treatment</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"c_flat,quantifoil,lacey_carbon,ultrathin_carbon,gold"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"plunge_freezing,high_pressure_freezing,slam_freezing"</formula1>
+    </dataValidation>
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"carbon,gold,graphene,silicon_nitride"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>method</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>crystallization_conditions</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>drop_volume</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>protein_concentration</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>crystal_size_um</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>cryo_protectant</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>crystal_id</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>screen_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>temperature_c</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>drop_ratio_protein_to_reservoir</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>reservoir_volume_ul</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>seeding_type</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>seed_stock_dilution</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"vapor_diffusion_hanging,vapor_diffusion_sitting,batch,microbatch,lcp,dialysis,free_interface_diffusion"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>protein_concentration_mg_per_ml</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>protein_buffer</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>additives</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>crystallization_method</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>crystallization_conditions</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>screen_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>temperature_c</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>drop_ratio_protein_to_reservoir</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>drop_volume_nl</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reservoir_volume_ul</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>seeding_type</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>seed_stock_dilution</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>initial_hit_condition</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>optimization_strategy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>optimized_condition</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>crystal_size_um</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>cryoprotectant</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>cryoprotectant_concentration</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>soak_compound</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>soak_conditions</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>mounting_method</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>flash_cooling_method</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>crystal_notes</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>loop_size</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>mounting_temperature</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"vapor_diffusion_hanging,vapor_diffusion_sitting,batch,microbatch,lcp,dialysis,free_interface_diffusion"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -5364,7 +5701,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5415,7 +5752,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5539,7 +5876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5720,7 +6057,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5761,7 +6098,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5812,215 +6149,6 @@
         </is>
       </c>
       <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>defocus_search_min</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>defocus_search_max</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>defocus_step</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>amplitude_contrast</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>cs_used_in_estimation</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>voltage_used_in_estimation</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>picking_method</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>box_size</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>power_score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ncc_score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>model_file_path</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>model_source</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>symmetry</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>box_size</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>gold_standard</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>split_strategy</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>resolution_0_143</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>resolution_0_5</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>map_sharpening_bfactor</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"C1,C2,C3,C4,C5,C6,C7,C8,C9,C10,D2,D3,D4,D5,D6,D7,D8,D9,D10,T,O,I"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>resolution_angstrom</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>fsc_value</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6123,37 +6251,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>defocus_search_min</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>sample_id</t>
+          <t>defocus_search_max</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>role</t>
+          <t>defocus_step</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>date_added</t>
+          <t>amplitude_contrast</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>cs_used_in_estimation</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>voltage_used_in_estimation</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"target,control,reference,blank"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6164,18 +6302,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>picking_method</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>experiment_id</t>
+          <t>box_size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>power_score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ncc_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>model_file_path</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>model_source</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
@@ -6190,18 +6363,89 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>study_id</t>
+          <t>symmetry</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>workflow_id</t>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>box_size</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>gold_standard</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>split_strategy</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>resolution_0_143</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>resolution_0_5</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>map_sharpening_bfactor</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"C1,C2,C3,C4,C5,C6,C7,C8,C9,C10,D2,D3,D4,D5,D6,D7,D8,D9,D10,T,O,I"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>resolution_angstrom</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>fsc_value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6454,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6222,7 +6466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>experiment_id</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -6237,50 +6481,14 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>preparation_id</t>
+          <t>date_added</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"target,buffer_blank,standard,size_marker"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>experiment_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>instrument_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"primary,detector,sample_handler"</formula1>
+      <formula1>"target,control,reference,blank"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6299,7 +6507,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>workflow_id</t>
+          <t>study_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -6314,6 +6522,73 @@
 </file>
 
 <file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>preparation_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"target,buffer_blank,standard,size_marker"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6325,37 +6600,37 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>workflow_id</t>
+          <t>experiment_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>file_id</t>
+          <t>instrument_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>input_type</t>
+          <t>role</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"raw_data,reference,parameters,mask"</formula1>
+      <formula1>"primary,detector,sample_handler"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6366,21 +6641,11 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>output_type</t>
+          <t>experiment_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"map,model,particles,micrographs,ctf_estimates,metadata,statistics,processed_data,log"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6511,6 +6776,78 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>input_type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"raw_data,reference,parameters,mask"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>output_type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"map,model,particles,micrographs,ctf_estimates,metadata,statistics,processed_data,log"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -63,21 +63,22 @@
     <sheet name="SAXSPreparation" sheetId="54" state="visible" r:id="rId54"/>
     <sheet name="ExperimentalConditions" sheetId="55" state="visible" r:id="rId55"/>
     <sheet name="DataCollectionStrategy" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="QualityMetrics" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="ComputeResources" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="MotionCorrectionParameters" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="CTFEstimationParameters" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="ParticlePickingParameters" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="RefinementParameters" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="FSCCurve" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="StudySampleAssociation" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="StudyExperimentAssociation" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="StudyWorkflowAssociation" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="ExperimentSampleAssociation" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="ExperimentInstrumentAssociation" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="WorkflowExperimentAssociation" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="WorkflowInputAssociation" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="WorkflowOutputAssociation" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="BeamCenterPixels" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="QualityMetrics" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="ComputeResources" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="MotionCorrectionParameters" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="CTFEstimationParameters" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="ParticlePickingParameters" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="RefinementParameters" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="FSCCurve" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="StudySampleAssociation" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="StudyExperimentAssociation" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="StudyWorkflowAssociation" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="ExperimentSampleAssociation" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="ExperimentInstrumentAssociation" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="WorkflowExperimentAssociation" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="WorkflowInputAssociation" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="WorkflowOutputAssociation" sheetId="72" state="visible" r:id="rId72"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3308,7 +3309,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG1"/>
+  <dimension ref="A1:BL1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3469,140 +3470,165 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>detector</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>wavelength</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
         <is>
           <t>oscillation_angle</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>start_angle</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>sweep_start</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>sweep_end</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
         <is>
           <t>number_of_images</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>beam_center_x</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>beam_center_y</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>beam_center_pixels</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>detector_distance</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>pixel_size_x</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>pixel_size_y</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>total_rotation</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>beamline</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>transmission</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>flux</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>flux_end</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>slit_gap_horizontal</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>slit_gap_vertical</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>undulator_gap</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>synchrotron_mode</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>exposure_time</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>start_time</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>end_time</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>resolution</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>resolution_at_corner</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>ispyb_data_collection_id</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>ispyb_session_id</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -5758,7 +5784,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5819,45 +5845,70 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>beam_center_pixels</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>beam_size_um</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>energy</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
         <is>
           <t>flux_photons_per_s</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>transmission_percent</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>attenuator</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>temperature_k</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>oscillation_per_image_deg</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>sweep_start</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>sweep_end</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
         <is>
           <t>total_rotation_deg</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
         <is>
           <t>strategy_notes</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -5877,6 +5928,37 @@
 </file>
 
 <file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>xbeam</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ybeam</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6057,7 +6139,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6088,67 +6170,6 @@
         </is>
       </c>
       <c r="E1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>patch_size</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>binning</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>dose_weighting</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>bfactor_dose_weighting</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>anisotropic_correction</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>frame_grouping</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>output_binning</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>drift_total</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6251,41 +6272,51 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>defocus_search_min</t>
+          <t>patch_size</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>defocus_search_max</t>
+          <t>binning</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>defocus_step</t>
+          <t>dose_weighting</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>amplitude_contrast</t>
+          <t>bfactor_dose_weighting</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>cs_used_in_estimation</t>
+          <t>anisotropic_correction</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>voltage_used_in_estimation</t>
+          <t>frame_grouping</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
+        <is>
+          <t>output_binning</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>drift_total</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6302,51 +6333,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>picking_method</t>
+          <t>defocus_search_min</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>box_size</t>
+          <t>defocus_search_max</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>threshold</t>
+          <t>defocus_step</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>power_score</t>
+          <t>amplitude_contrast</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ncc_score</t>
+          <t>cs_used_in_estimation</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>model_name</t>
+          <t>voltage_used_in_estimation</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>model_file_path</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>model_source</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6369,6 +6390,67 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>picking_method</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>box_size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>power_score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ncc_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>model_file_path</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>model_source</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>symmetry</t>
         </is>
       </c>
@@ -6423,7 +6505,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6454,7 +6536,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6491,32 +6573,6 @@
       <formula1>"target,control,reference,blank"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>study_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>experiment_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6538,7 +6594,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>workflow_id</t>
+          <t>experiment_id</t>
         </is>
       </c>
     </row>
@@ -6548,6 +6604,32 @@
 </file>
 
 <file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6588,7 +6670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6620,32 +6702,6 @@
       <formula1>"primary,detector,sample_handler"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>workflow_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>experiment_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6782,7 +6838,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6793,21 +6849,11 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>input_type</t>
+          <t>experiment_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"raw_data,reference,parameters,mask"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6834,6 +6880,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>input_type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"raw_data,reference,parameters,mask"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>output_type</t>
         </is>
       </c>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -2180,7 +2180,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2191,55 +2191,60 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>instrument_registry_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>instrument_category</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>facility_ror</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2247,13 +2252,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
     </dataValidation>
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2267,7 +2272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL1"/>
+  <dimension ref="A1:AM1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2408,55 +2413,60 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>instrument_registry_id</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
           <t>instrument_category</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>facility_ror</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2473,13 +2483,13 @@
     <dataValidation sqref="Y2:Y1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"EFTEM,TEM,STEM"</formula1>
     </dataValidation>
-    <dataValidation sqref="AB2:AB1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC2:AC1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AD2:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="AI2:AI1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AJ2:AJ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2493,7 +2503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2564,55 +2574,60 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>instrument_registry_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>instrument_category</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>facility_ror</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2626,13 +2641,13 @@
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"direct_electron_detector,ccd,cmos,hybrid_photon_counting,scintillator_coupled,imaging_plate,film"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2905,7 +2920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2951,55 +2966,60 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>instrument_registry_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>instrument_category</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>facility_ror</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3010,13 +3030,13 @@
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3030,7 +3050,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3071,55 +3091,60 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>instrument_registry_id</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>instrument_category</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>facility_ror</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3127,13 +3152,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation sqref="H2:H1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
     </dataValidation>
-    <dataValidation sqref="I2:I1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3147,7 +3172,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3218,55 +3243,60 @@
       </c>
       <c r="N1" t="inlineStr">
         <is>
+          <t>instrument_registry_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
           <t>instrument_category</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>facility_name</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>facility_ror</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3289,13 +3319,13 @@
     <dataValidation sqref="L2:L1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"epics,tango,labview,opi"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="U2:U1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="V2:V1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3309,7 +3339,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BL1"/>
+  <dimension ref="A1:BK1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3545,90 +3575,85 @@
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>beamline</t>
+          <t>transmission</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>transmission</t>
+          <t>flux</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>flux</t>
+          <t>flux_end</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>flux_end</t>
+          <t>slit_gap_horizontal</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>slit_gap_horizontal</t>
+          <t>slit_gap_vertical</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>slit_gap_vertical</t>
+          <t>undulator_gap</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>undulator_gap</t>
+          <t>synchrotron_mode</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>synchrotron_mode</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>exposure_time</t>
+          <t>start_time</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>start_time</t>
+          <t>end_time</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>end_time</t>
+          <t>resolution</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>resolution</t>
+          <t>resolution_at_corner</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>resolution_at_corner</t>
+          <t>ispyb_data_collection_id</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>ispyb_data_collection_id</t>
+          <t>ispyb_session_id</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>ispyb_session_id</t>
+          <t>id</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>title</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="BL1" t="inlineStr">
         <is>
           <t>description</t>
         </is>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -66,19 +66,20 @@
     <sheet name="BeamCenterPixels" sheetId="57" state="visible" r:id="rId57"/>
     <sheet name="QualityMetrics" sheetId="58" state="visible" r:id="rId58"/>
     <sheet name="ComputeResources" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="MotionCorrectionParameters" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="CTFEstimationParameters" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="ParticlePickingParameters" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="RefinementParameters" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="FSCCurve" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="StudySampleAssociation" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="StudyExperimentAssociation" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="StudyWorkflowAssociation" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="ExperimentSampleAssociation" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="ExperimentInstrumentAssociation" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="WorkflowExperimentAssociation" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="WorkflowInputAssociation" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="WorkflowOutputAssociation" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="CryoEMQualityMetrics" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="MotionCorrectionParameters" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="CTFEstimationParameters" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="ParticlePickingParameters" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="RefinementParameters" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="FSCCurve" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="StudySampleAssociation" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="StudyExperimentAssociation" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="StudyWorkflowAssociation" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="ExperimentSampleAssociation" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="ExperimentInstrumentAssociation" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="WorkflowExperimentAssociation" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="WorkflowInputAssociation" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="WorkflowOutputAssociation" sheetId="73" state="visible" r:id="rId73"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1565,26 +1566,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>proposal_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>keywords</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3028,7 +3034,7 @@
   </sheetData>
   <dataValidations count="4">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography,microed"</formula1>
     </dataValidation>
     <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"SYNCHROTRON_BEAMLINE,NEUTRON_BEAMLINE,XFEL_BEAMLINE,ELECTRON_MICROSCOPE,BENCHTOP_XRAY,OPTICAL_MICROSCOPE,SPECTROMETER"</formula1>
@@ -3305,7 +3311,7 @@
   </sheetData>
   <dataValidations count="8">
     <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography,microed"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"synchrotron,rotating_anode,microfocus,metal_jet"</formula1>
@@ -3339,7 +3345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BK1"/>
+  <dimension ref="A1:BW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3475,194 +3481,254 @@
       </c>
       <c r="AA1" t="inlineStr">
         <is>
+          <t>tilting_scheme</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>tilt_angle_min</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>tilt_angle_max</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>tilt_angle_increment</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>tilt_axis_angle</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>number_of_tilt_images</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>dose_per_tilt</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>dual_tilt_axis_rotation</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>fiducial_size</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>rotation_rate</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>camera_length</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>frames_per_second</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
           <t>autoloader_slot</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>shots_per_hole</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AO1" t="inlineStr">
         <is>
           <t>holes_per_group</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AP1" t="inlineStr">
         <is>
           <t>acquisition_software</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AQ1" t="inlineStr">
         <is>
           <t>acquisition_software_version</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AR1" t="inlineStr">
         <is>
           <t>detector</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AS1" t="inlineStr">
         <is>
           <t>wavelength</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AT1" t="inlineStr">
         <is>
           <t>energy</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AU1" t="inlineStr">
         <is>
           <t>oscillation_angle</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AV1" t="inlineStr">
         <is>
           <t>start_angle</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AW1" t="inlineStr">
         <is>
           <t>sweep_start</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AX1" t="inlineStr">
         <is>
           <t>sweep_end</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AY1" t="inlineStr">
         <is>
           <t>number_of_images</t>
         </is>
       </c>
-      <c r="AN1" t="inlineStr">
+      <c r="AZ1" t="inlineStr">
         <is>
           <t>beam_center_x</t>
         </is>
       </c>
-      <c r="AO1" t="inlineStr">
+      <c r="BA1" t="inlineStr">
         <is>
           <t>beam_center_y</t>
         </is>
       </c>
-      <c r="AP1" t="inlineStr">
+      <c r="BB1" t="inlineStr">
         <is>
           <t>beam_center_pixels</t>
         </is>
       </c>
-      <c r="AQ1" t="inlineStr">
+      <c r="BC1" t="inlineStr">
         <is>
           <t>detector_distance</t>
         </is>
       </c>
-      <c r="AR1" t="inlineStr">
+      <c r="BD1" t="inlineStr">
         <is>
           <t>pixel_size_x</t>
         </is>
       </c>
-      <c r="AS1" t="inlineStr">
+      <c r="BE1" t="inlineStr">
         <is>
           <t>pixel_size_y</t>
         </is>
       </c>
-      <c r="AT1" t="inlineStr">
+      <c r="BF1" t="inlineStr">
         <is>
           <t>total_rotation</t>
         </is>
       </c>
-      <c r="AU1" t="inlineStr">
+      <c r="BG1" t="inlineStr">
         <is>
           <t>transmission</t>
         </is>
       </c>
-      <c r="AV1" t="inlineStr">
+      <c r="BH1" t="inlineStr">
         <is>
           <t>flux</t>
         </is>
       </c>
-      <c r="AW1" t="inlineStr">
+      <c r="BI1" t="inlineStr">
         <is>
           <t>flux_end</t>
         </is>
       </c>
-      <c r="AX1" t="inlineStr">
+      <c r="BJ1" t="inlineStr">
         <is>
           <t>slit_gap_horizontal</t>
         </is>
       </c>
-      <c r="AY1" t="inlineStr">
+      <c r="BK1" t="inlineStr">
         <is>
           <t>slit_gap_vertical</t>
         </is>
       </c>
-      <c r="AZ1" t="inlineStr">
+      <c r="BL1" t="inlineStr">
         <is>
           <t>undulator_gap</t>
         </is>
       </c>
-      <c r="BA1" t="inlineStr">
+      <c r="BM1" t="inlineStr">
         <is>
           <t>synchrotron_mode</t>
         </is>
       </c>
-      <c r="BB1" t="inlineStr">
+      <c r="BN1" t="inlineStr">
         <is>
           <t>exposure_time</t>
         </is>
       </c>
-      <c r="BC1" t="inlineStr">
+      <c r="BO1" t="inlineStr">
         <is>
           <t>start_time</t>
         </is>
       </c>
-      <c r="BD1" t="inlineStr">
+      <c r="BP1" t="inlineStr">
         <is>
           <t>end_time</t>
         </is>
       </c>
-      <c r="BE1" t="inlineStr">
+      <c r="BQ1" t="inlineStr">
         <is>
           <t>resolution</t>
         </is>
       </c>
-      <c r="BF1" t="inlineStr">
+      <c r="BR1" t="inlineStr">
         <is>
           <t>resolution_at_corner</t>
         </is>
       </c>
-      <c r="BG1" t="inlineStr">
+      <c r="BS1" t="inlineStr">
         <is>
           <t>ispyb_data_collection_id</t>
         </is>
       </c>
-      <c r="BH1" t="inlineStr">
+      <c r="BT1" t="inlineStr">
         <is>
           <t>ispyb_session_id</t>
         </is>
       </c>
-      <c r="BI1" t="inlineStr">
+      <c r="BU1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="BJ1" t="inlineStr">
+      <c r="BV1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="BK1" t="inlineStr">
+      <c r="BW1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography"</formula1>
+      <formula1>"cryo_em,xray_crystallography,saxs,waxs,sans,cryo_et,electron_microscopy,mass_spectrometry,xas,xanes,exafs,xmcd,neutron_crystallography,fiber_diffraction,time_resolved_crystallography,xray_tomography,microed"</formula1>
     </dataValidation>
     <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"x_ray_diffraction,neutron_diffraction,electron_diffraction,fiber_diffraction"</formula1>
@@ -3672,6 +3738,9 @@
     </dataValidation>
     <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"bluesky,spec,sardana,gda,mxcube_daq,blu_ice,jblue_ice"</formula1>
+    </dataValidation>
+    <dataValidation sqref="AA2:AA1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"none,dose_symmetric,linear,continuous"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5989,7 +6058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG1"/>
+  <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6150,10 +6219,15 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>cryo_em</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>r_factor</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6297,6 +6371,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ice_contamination</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ice_quality</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>particle_concentration</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="3">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"none,limited,severe"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"ideal,too_thin,too_thick"</formula1>
+    </dataValidation>
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"optimal,too_low,too_high"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -6352,7 +6473,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6393,67 +6514,6 @@
         </is>
       </c>
       <c r="G1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:I1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>picking_method</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>box_size</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>threshold</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>power_score</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>ncc_score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>model_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>model_file_path</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>model_source</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6476,6 +6536,67 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>picking_method</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>box_size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>threshold</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>power_score</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>ncc_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>model_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>model_file_path</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>model_source</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
           <t>symmetry</t>
         </is>
       </c>
@@ -6530,7 +6651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6561,7 +6682,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6598,32 +6719,6 @@
       <formula1>"target,control,reference,blank"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>study_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>experiment_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6645,7 +6740,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>workflow_id</t>
+          <t>experiment_id</t>
         </is>
       </c>
     </row>
@@ -6655,6 +6750,32 @@
 </file>
 
 <file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6689,42 +6810,6 @@
   <dataValidations count="1">
     <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"target,buffer_blank,standard,size_marker"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>experiment_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>instrument_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"primary,detector,sample_handler"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6863,22 +6948,32 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>workflow_id</t>
+          <t>experiment_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>experiment_id</t>
+          <t>instrument_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"primary,detector,sample_handler"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6889,7 +6984,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6900,21 +6995,11 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>file_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>input_type</t>
+          <t>experiment_id</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"raw_data,reference,parameters,mask"</formula1>
-    </dataValidation>
-  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6941,6 +7026,42 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>input_type</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"raw_data,reference,parameters,mask"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>file_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>output_type</t>
         </is>
       </c>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -6219,7 +6219,7 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>cryo_em</t>
+          <t>grid_quality</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -28,57 +28,64 @@
     <sheet name="MeasurementConditions" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Dataset" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Study" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="Sample" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="ProteinConstruct" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="SamplePreparation" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="Instrument" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="CryoEMInstrument" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="XRayInstrument" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="SANSDetector" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="SANSSource" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="SANSConfiguration" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="SANSInstrument" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="SAXSInstrument" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="BeamlineInstrument" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="ExperimentRun" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="WorkflowRun" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="DataFile" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="Image" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="Image2D" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Image3D" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="Movie" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="Micrograph" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="FTIRImage" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="FluorescenceImage" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="OpticalImage" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="XRFImage" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="ImageFeature" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="OntologyTerm" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="MolecularComposition" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="BufferComposition" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="StorageConditions" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="CryoEMPreparation" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="CrystallizationConditions" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="XRayPreparation" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="SAXSPreparation" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="ExperimentalConditions" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="DataCollectionStrategy" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="BeamCenterPixels" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="QualityMetrics" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="ComputeResources" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="MotionCorrectionParameters" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="CTFEstimationParameters" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="ParticlePickingParameters" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="RefinementParameters" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="FSCCurve" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="StudySampleAssociation" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="StudyExperimentAssociation" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="StudyWorkflowAssociation" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="ExperimentSampleAssociation" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="ExperimentInstrumentAssociation" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="WorkflowExperimentAssociation" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="WorkflowInputAssociation" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="WorkflowOutputAssociation" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="Person" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Organization" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="Sample" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="ProteinConstruct" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="SamplePreparation" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="Instrument" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="CryoEMInstrument" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="XRayInstrument" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="SANSDetector" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="SANSSource" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="SANSConfiguration" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="SANSInstrument" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="SAXSInstrument" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="BeamlineInstrument" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="ExperimentRun" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="WorkflowRun" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="DataFile" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="Image" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Image2D" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Image3D" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Movie" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Micrograph" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="FTIRImage" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="FluorescenceImage" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="OpticalImage" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="XRFImage" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="ImageFeature" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="OntologyTerm" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="MolecularComposition" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="BufferComposition" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="StorageConditions" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="CryoEMPreparation" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="CrystallizationConditions" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="XRayPreparation" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="SAXSPreparation" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="ExperimentalConditions" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="DataCollectionStrategy" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="BeamCenterPixels" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="QualityMetrics" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="ComputeResources" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="MotionCorrectionParameters" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="CTFEstimationParameters" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="ParticlePickingParameters" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="RefinementParameters" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="FSCCurve" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="StudySampleAssociation" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="StudyExperimentAssociation" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="StudyWorkflowAssociation" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="ExperimentSampleAssociation" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="ExperimentInstrumentAssociation" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="WorkflowExperimentAssociation" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="WorkflowInputAssociation" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="WorkflowOutputAssociation" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="StudyPersonAssociation" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="ExperimentPersonAssociation" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="WorkflowPersonAssociation" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="StudyOrganizationAssociation" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="PersonOrganizationAssociation" sheetId="79" state="visible" r:id="rId79"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1444,7 +1451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U1"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1460,142 +1467,350 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>persons</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>organizations</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>instruments</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>protein_constructs</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>samples</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sample_preparations</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>experiment_runs</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>workflow_runs</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>data_files</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>images</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>study_sample_associations</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>study_experiment_associations</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>study_workflow_associations</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>experiment_sample_associations</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>experiment_instrument_associations</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>workflow_experiment_associations</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>workflow_input_associations</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>workflow_output_associations</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>study_person_associations</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>experiment_person_associations</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>workflow_person_associations</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>study_organization_associations</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>person_organization_associations</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>keywords</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>protein_constructs</t>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>orcid</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>given_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>family_name</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>samples</t>
+          <t>email</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>sample_preparations</t>
+          <t>affiliation</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>experiment_runs</t>
+          <t>affiliation_ror</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>workflow_runs</t>
+          <t>person_local_id</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>data_files</t>
+          <t>id</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>images</t>
+          <t>title</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>study_sample_associations</t>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>ror</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>acronym</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>organization_type</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>facility_code</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>facility_type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>parent_organization_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>website</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>wikidata_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>is_doe_facility</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>study_experiment_associations</t>
+          <t>doe_office</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>study_workflow_associations</t>
+          <t>id</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>experiment_sample_associations</t>
+          <t>title</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>experiment_instrument_associations</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>workflow_experiment_associations</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>workflow_input_associations</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>workflow_output_associations</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
           <t>description</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>keywords</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+  <dataValidations count="3">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"national_laboratory,university,research_institute,government_agency,funding_agency,company,hospital,consortium,other"</formula1>
+    </dataValidation>
+    <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
+    </dataValidation>
+    <dataValidation sqref="E2:E1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"SYNCHROTRON,NEUTRON_SOURCE,FREE_ELECTRON_LASER,CRYOEM_CENTER"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1786,7 +2001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1922,7 +2137,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2174,13 +2389,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2211,40 +2426,45 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>facility_organization_id</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2258,7 +2478,7 @@
     <dataValidation sqref="D2:D1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2266,13 +2486,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AM1"/>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2433,40 +2653,45 @@
       </c>
       <c r="AF1" t="inlineStr">
         <is>
+          <t>facility_organization_id</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="AG1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="AH1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="AI1" t="inlineStr">
+      <c r="AJ1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="AJ1" t="inlineStr">
+      <c r="AK1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="AK1" t="inlineStr">
+      <c r="AL1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AL1" t="inlineStr">
+      <c r="AM1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="AM1" t="inlineStr">
+      <c r="AN1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2489,7 +2714,7 @@
     <dataValidation sqref="AD2:AD1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="AJ2:AJ1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="AK2:AK1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2497,13 +2722,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y1"/>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2594,40 +2819,45 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>facility_organization_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2647,7 +2877,7 @@
     <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -2655,7 +2885,58 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>maximum_numeric_value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>minimum_numeric_value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>numeric_value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit_cv_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>raw_value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2726,7 +3007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2782,244 +3063,198 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>maximum_numeric_value</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>minimum_numeric_value</t>
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>q_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_max</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>numeric_value</t>
+          <t>number_of_guides</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>attenuator</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>unit_cv_id</t>
+          <t>source_aperature_diameter</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>attribute</t>
+          <t>sample_aperature_diameter</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>raw_value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>q_min</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>q_max</t>
+          <t>siwindow_to_main_distance</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sample_ap_to_si_distance</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>sample_ap_to_main_distance</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>sample_ap_to_sample_distance</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>source_ap_to_siwindow_distance</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source_ap_to_sample_ap_distance</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>technique</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_range_min</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>number_of_guides</t>
+          <t>q_range_max</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>attenuator</t>
+          <t>detectors</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>source_aperature_diameter</t>
+          <t>source</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>sample_aperature_diameter</t>
+          <t>configuration</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>siwindow_to_main_distance</t>
+          <t>environment</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>sample_ap_to_si_distance</t>
+          <t>instrument_code</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>sample_ap_to_main_distance</t>
+          <t>instrument_registry_id</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>sample_ap_to_sample_distance</t>
+          <t>instrument_category</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>source_ap_to_siwindow_distance</t>
+          <t>facility_name</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>source_ap_to_sample_ap_distance</t>
+          <t>facility_ror</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:T1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>technique</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>q_range_min</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>q_range_max</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>detectors</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>source</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>configuration</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>environment</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>instrument_code</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>instrument_registry_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>instrument_category</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>facility_name</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>facility_ror</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
+          <t>facility_organization_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
         <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3036,7 +3271,7 @@
     <dataValidation sqref="K2:K1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="R2:R1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3044,13 +3279,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:S1"/>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3111,40 +3346,45 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
+          <t>facility_organization_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3158,7 +3398,7 @@
     <dataValidation sqref="J2:J1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="Q2:Q1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3166,13 +3406,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Y1"/>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3263,40 +3503,45 @@
       </c>
       <c r="R1" t="inlineStr">
         <is>
+          <t>facility_organization_id</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
           <t>beamline_id</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>installation_date</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>current_status</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -3325,7 +3570,7 @@
     <dataValidation sqref="P2:P1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"NSLS_II,ALS,SSRL,ESRF,DIAMOND,PHOTON_FACTORY,APS,SPRING8,PETRA_III,SOLEIL,AUSTRALIAN_SYNCHROTRON,EMSL,SNS,HFIR"</formula1>
     </dataValidation>
-    <dataValidation sqref="V2:V1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="W2:W1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"operational,maintenance,offline,commissioning"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3333,7 +3578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3678,7 +3923,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4039,7 +4284,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4128,7 +4373,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4194,7 +4439,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value_cv_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>raw_value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4270,7 +4551,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4351,184 +4632,476 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value_cv_id</t>
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>frames</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>super_resolution</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>attribute</t>
+          <t>pixel_size_unbinned</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>raw_value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>frames</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>super_resolution</t>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stage_position_x</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>stage_position_y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stage_position_z</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>nominal_defocus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dose_per_frame</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>beam_shift_x</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>beam_shift_y</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ice_thickness_estimate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>grid_square_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>hole_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>acquisition_group</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>origin_movie_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>pixel_size_unbinned</t>
+          <t>defocus_u</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>timestamp</t>
+          <t>defocus_v</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>stage_position_x</t>
+          <t>astigmatism_angle</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>stage_position_y</t>
+          <t>resolution_fit_limit</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>stage_position_z</t>
+          <t>ctf_quality_score</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>nominal_defocus</t>
+          <t>defocus</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>dose_per_frame</t>
+          <t>astigmatism</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>beam_shift_x</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>beam_shift_y</t>
+          <t>acquisition_date</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>ice_thickness_estimate</t>
+          <t>pixel_size</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>grid_square_id</t>
+          <t>dimensions_x</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>hole_id</t>
+          <t>dimensions_y</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>acquisition_group</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>wavenumber_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>wavenumber_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spectral_resolution</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>number_of_scans</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>apodization_function</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>molecular_signatures</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>background_correction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>excitation_wavelength</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>emission_wavelength</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>excitation_filter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>emission_filter</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>fluorophore</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>channel_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>laser_power</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pinhole_size</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>quantum_yield</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>defocus</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>astigmatism</t>
+          <t>exposure_time</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>file_name</t>
+          <t>dose</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>acquisition_date</t>
+          <t>id</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>pixel_size</t>
+          <t>title</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
           <t>description</t>
         </is>
       </c>
@@ -4538,335 +5111,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>origin_movie_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>defocus_u</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>defocus_v</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>astigmatism_angle</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>resolution_fit_limit</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ctf_quality_score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>wavenumber_min</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>wavenumber_max</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>spectral_resolution</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>number_of_scans</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>apodization_function</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>molecular_signatures</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>background_correction</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>excitation_wavelength</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>emission_wavelength</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>excitation_filter</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>emission_filter</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>fluorophore</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>channel_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>laser_power</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pinhole_size</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>quantum_yield</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4977,7 +5222,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5106,7 +5351,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5132,7 +5377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5183,7 +5428,38 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>raw_value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5219,7 +5495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5255,59 +5531,28 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>attribute</t>
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>duration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>raw_value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
           <t>atmosphere</t>
         </is>
       </c>
@@ -5322,7 +5567,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5464,7 +5709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5555,7 +5800,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5706,7 +5951,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5752,7 +5997,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5803,7 +6048,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5952,7 +6197,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5973,228 +6218,6 @@
         </is>
       </c>
       <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AG1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>resolution</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>resolution_high_shell_a</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>resolution_low_a</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>completeness</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>completeness_high_res_shell_percent</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>signal_to_noise</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>mean_i_over_sigma_i</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>space_group</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>unit_cell_a</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>unit_cell_b</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>unit_cell_c</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>unit_cell_alpha</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>unit_cell_beta</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>unit_cell_gamma</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>multiplicity</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>cc_half</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>r_merge</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>r_pim</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>wilson_b_factor_a2</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>anomalous_used</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>anom_corr</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>anom_sig_ano</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>r_work</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>r_free</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>ramachandran_favored_percent</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>ramachandran_outliers_percent</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>clashscore</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>molprobity_score</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>average_b_factor_a2</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>i_zero</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>rg</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
-        <is>
-          <t>r_factor</t>
-        </is>
-      </c>
-      <c r="AG1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>cpu_hours</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>gpu_hours</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>memory_gb</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>storage_gb</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -6297,6 +6320,228 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:AG1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>resolution</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>resolution_high_shell_a</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>resolution_low_a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>completeness</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>completeness_high_res_shell_percent</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>signal_to_noise</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mean_i_over_sigma_i</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>space_group</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>unit_cell_a</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>unit_cell_b</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>unit_cell_c</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>unit_cell_alpha</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>unit_cell_beta</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>unit_cell_gamma</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>multiplicity</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>cc_half</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>r_merge</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>r_pim</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>wilson_b_factor_a2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>anomalous_used</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>anom_corr</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>anom_sig_ano</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>r_work</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>r_free</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>ramachandran_favored_percent</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>ramachandran_outliers_percent</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>clashscore</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>molprobity_score</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>average_b_factor_a2</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>i_zero</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>rg</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>r_factor</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>cpu_hours</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>gpu_hours</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>memory_gb</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>storage_gb</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:I1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -6352,7 +6597,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6403,7 +6648,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6464,7 +6709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6530,7 +6775,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6561,7 +6806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6602,7 +6847,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6628,7 +6873,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6654,7 +6899,133 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>site_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>site_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>residues</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ligand_interactions</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>conservation_score</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>functional_importance</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>go_terms</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ec_number</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6695,7 +7066,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6731,133 +7102,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>site_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>site_name</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>residues</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>ligand_interactions</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>conservation_score</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>functional_importance</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>go_terms</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>ec_number</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>protein_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pdb_entry</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>chain_id</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>residue_range</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>confidence_score</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>evidence_code</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>source_database</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>annotation_method</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>publication_ids</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation sqref="N2:N1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet70.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6883,7 +7128,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6919,7 +7164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6955,6 +7200,211 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>person_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>author_position</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>corresponding</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"principal_investigator,co_investigator,author,operator,local_contact,analyst,reviewer,data_curator,submitter,contact"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>person_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"principal_investigator,co_investigator,author,operator,local_contact,analyst,reviewer,data_curator,submitter,contact"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>workflow_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>person_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"principal_investigator,co_investigator,author,operator,local_contact,analyst,reviewer,data_curator,submitter,contact"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>award_number</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"host_institution,operating_institution,funder,collaborating_institution,depositor,primary_affiliation,secondary_affiliation,former_affiliation"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>person_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>organization_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>start_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>end_date</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"host_institution,operating_institution,funder,collaborating_institution,depositor,primary_affiliation,secondary_affiliation,former_affiliation"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/assets/excel/lambda_ber_schema.xlsx
+++ b/assets/excel/lambda_ber_schema.xlsx
@@ -31,62 +31,64 @@
     <sheet name="Person" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="Organization" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="Sample" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="ProteinConstruct" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="SamplePreparation" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="Instrument" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="CryoEMInstrument" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="XRayInstrument" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="SANSDetector" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="SANSSource" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="SANSConfiguration" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="SANSInstrument" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="SAXSInstrument" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="BeamlineInstrument" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="ExperimentRun" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="WorkflowRun" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="DataFile" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="Image" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="Image2D" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="Image3D" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="Movie" sheetId="42" state="visible" r:id="rId42"/>
-    <sheet name="Micrograph" sheetId="43" state="visible" r:id="rId43"/>
-    <sheet name="FTIRImage" sheetId="44" state="visible" r:id="rId44"/>
-    <sheet name="FluorescenceImage" sheetId="45" state="visible" r:id="rId45"/>
-    <sheet name="OpticalImage" sheetId="46" state="visible" r:id="rId46"/>
-    <sheet name="XRFImage" sheetId="47" state="visible" r:id="rId47"/>
-    <sheet name="ImageFeature" sheetId="48" state="visible" r:id="rId48"/>
-    <sheet name="OntologyTerm" sheetId="49" state="visible" r:id="rId49"/>
-    <sheet name="MolecularComposition" sheetId="50" state="visible" r:id="rId50"/>
-    <sheet name="BufferComposition" sheetId="51" state="visible" r:id="rId51"/>
-    <sheet name="StorageConditions" sheetId="52" state="visible" r:id="rId52"/>
-    <sheet name="CryoEMPreparation" sheetId="53" state="visible" r:id="rId53"/>
-    <sheet name="CrystallizationConditions" sheetId="54" state="visible" r:id="rId54"/>
-    <sheet name="XRayPreparation" sheetId="55" state="visible" r:id="rId55"/>
-    <sheet name="SAXSPreparation" sheetId="56" state="visible" r:id="rId56"/>
-    <sheet name="ExperimentalConditions" sheetId="57" state="visible" r:id="rId57"/>
-    <sheet name="DataCollectionStrategy" sheetId="58" state="visible" r:id="rId58"/>
-    <sheet name="BeamCenterPixels" sheetId="59" state="visible" r:id="rId59"/>
-    <sheet name="QualityMetrics" sheetId="60" state="visible" r:id="rId60"/>
-    <sheet name="ComputeResources" sheetId="61" state="visible" r:id="rId61"/>
-    <sheet name="CryoEMQualityMetrics" sheetId="62" state="visible" r:id="rId62"/>
-    <sheet name="MotionCorrectionParameters" sheetId="63" state="visible" r:id="rId63"/>
-    <sheet name="CTFEstimationParameters" sheetId="64" state="visible" r:id="rId64"/>
-    <sheet name="ParticlePickingParameters" sheetId="65" state="visible" r:id="rId65"/>
-    <sheet name="RefinementParameters" sheetId="66" state="visible" r:id="rId66"/>
-    <sheet name="FSCCurve" sheetId="67" state="visible" r:id="rId67"/>
-    <sheet name="StudySampleAssociation" sheetId="68" state="visible" r:id="rId68"/>
-    <sheet name="StudyExperimentAssociation" sheetId="69" state="visible" r:id="rId69"/>
-    <sheet name="StudyWorkflowAssociation" sheetId="70" state="visible" r:id="rId70"/>
-    <sheet name="ExperimentSampleAssociation" sheetId="71" state="visible" r:id="rId71"/>
-    <sheet name="ExperimentInstrumentAssociation" sheetId="72" state="visible" r:id="rId72"/>
-    <sheet name="WorkflowExperimentAssociation" sheetId="73" state="visible" r:id="rId73"/>
-    <sheet name="WorkflowInputAssociation" sheetId="74" state="visible" r:id="rId74"/>
-    <sheet name="WorkflowOutputAssociation" sheetId="75" state="visible" r:id="rId75"/>
-    <sheet name="StudyPersonAssociation" sheetId="76" state="visible" r:id="rId76"/>
-    <sheet name="ExperimentPersonAssociation" sheetId="77" state="visible" r:id="rId77"/>
-    <sheet name="WorkflowPersonAssociation" sheetId="78" state="visible" r:id="rId78"/>
-    <sheet name="StudyOrganizationAssociation" sheetId="79" state="visible" r:id="rId79"/>
-    <sheet name="PersonOrganizationAssociation" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="Protein" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="ProteinConstruct" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="SamplePreparation" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="Instrument" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="CryoEMInstrument" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="XRayInstrument" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="SANSDetector" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="SANSSource" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="SANSConfiguration" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="SANSInstrument" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="SAXSInstrument" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="BeamlineInstrument" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="ExperimentRun" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet name="WorkflowRun" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet name="DataFile" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet name="Image" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet name="Image2D" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet name="Image3D" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet name="Movie" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet name="Micrograph" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet name="FTIRImage" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet name="FluorescenceImage" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet name="OpticalImage" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet name="XRFImage" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet name="ImageFeature" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet name="OntologyTerm" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet name="MolecularComposition" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet name="BufferComposition" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet name="StorageConditions" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet name="CryoEMPreparation" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet name="CrystallizationConditions" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet name="XRayPreparation" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet name="SAXSPreparation" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet name="ExperimentalConditions" sheetId="58" state="visible" r:id="rId58"/>
+    <sheet name="DataCollectionStrategy" sheetId="59" state="visible" r:id="rId59"/>
+    <sheet name="BeamCenterPixels" sheetId="60" state="visible" r:id="rId60"/>
+    <sheet name="QualityMetrics" sheetId="61" state="visible" r:id="rId61"/>
+    <sheet name="ComputeResources" sheetId="62" state="visible" r:id="rId62"/>
+    <sheet name="CryoEMQualityMetrics" sheetId="63" state="visible" r:id="rId63"/>
+    <sheet name="MotionCorrectionParameters" sheetId="64" state="visible" r:id="rId64"/>
+    <sheet name="CTFEstimationParameters" sheetId="65" state="visible" r:id="rId65"/>
+    <sheet name="ParticlePickingParameters" sheetId="66" state="visible" r:id="rId66"/>
+    <sheet name="RefinementParameters" sheetId="67" state="visible" r:id="rId67"/>
+    <sheet name="FSCCurve" sheetId="68" state="visible" r:id="rId68"/>
+    <sheet name="StudySampleAssociation" sheetId="69" state="visible" r:id="rId69"/>
+    <sheet name="StudyExperimentAssociation" sheetId="70" state="visible" r:id="rId70"/>
+    <sheet name="StudyWorkflowAssociation" sheetId="71" state="visible" r:id="rId71"/>
+    <sheet name="ExperimentSampleAssociation" sheetId="72" state="visible" r:id="rId72"/>
+    <sheet name="SampleProteinAssociation" sheetId="73" state="visible" r:id="rId73"/>
+    <sheet name="ExperimentInstrumentAssociation" sheetId="74" state="visible" r:id="rId74"/>
+    <sheet name="WorkflowExperimentAssociation" sheetId="75" state="visible" r:id="rId75"/>
+    <sheet name="WorkflowInputAssociation" sheetId="76" state="visible" r:id="rId76"/>
+    <sheet name="WorkflowOutputAssociation" sheetId="77" state="visible" r:id="rId77"/>
+    <sheet name="StudyPersonAssociation" sheetId="78" state="visible" r:id="rId78"/>
+    <sheet name="ExperimentPersonAssociation" sheetId="79" state="visible" r:id="rId79"/>
+    <sheet name="WorkflowPersonAssociation" sheetId="80" state="visible" r:id="rId80"/>
+    <sheet name="StudyOrganizationAssociation" sheetId="81" state="visible" r:id="rId81"/>
+    <sheet name="PersonOrganizationAssociation" sheetId="82" state="visible" r:id="rId82"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1452,7 +1454,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AD1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1483,115 +1485,125 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>proteins</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>protein_constructs</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>samples</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>sample_preparations</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>experiment_runs</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>workflow_runs</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>data_files</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>images</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>study_sample_associations</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>study_experiment_associations</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>study_workflow_associations</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>experiment_sample_associations</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>experiment_instrument_associations</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>sample_protein_associations</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
         <is>
           <t>workflow_experiment_associations</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>workflow_input_associations</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>workflow_output_associations</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>study_person_associations</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>experiment_person_associations</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>workflow_person_associations</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>study_organization_associations</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>person_organization_associations</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2013,7 +2025,148 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X1"/>
+  <dimension ref="A1:Y1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>uniprot_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>protein_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>gene_name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>organism</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>organism_name</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>amino_acid_sequence</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sequence_length</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>molecular_weight_theoretical</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>ec_numbers</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>function_description</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>go_terms</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pdb_entries</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>functional_sites</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>structural_features</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>protein_interactions</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ligand_interactions</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>mutation_effects</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ptm_annotations</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>biophysical_properties</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>evolutionary_conservation</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>conformational_ensemble</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>cross_references</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Y1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2024,115 +2177,120 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>uniprot_id</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gene_name</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ncbi_taxid</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>sequence_length_aa</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>construct_description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>gene_synthesis_provider</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>codon_optimization_organism</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>vector_backbone</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>vector_name</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>promoter</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>tag_nterm</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>tag_cterm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>cleavage_site</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>signal_peptide</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>selectable_marker</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>cloning_method</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>insert_boundaries</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>sequence_file_path</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>sequence_verified_by</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>verification_notes</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -2143,7 +2301,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2395,7 +2553,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2492,7 +2650,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2728,7 +2886,58 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>maximum_numeric_value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>minimum_numeric_value</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>numeric_value</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>unit</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit_cv_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>raw_value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2891,119 +3100,205 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>maximum_numeric_value</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>minimum_numeric_value</t>
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>detector_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>detector_type</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>numeric_value</t>
+          <t>detector_description</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>unit</t>
+          <t>pixel_size_x</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>unit_cv_id</t>
+          <t>pixel_size_y</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>attribute</t>
+          <t>sample_detector_distance</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>raw_value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>detector_name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>detector_type</t>
+          <t>rotation_angle</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>beam_trap_type</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>beam_trap_position_x</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>beam_trap_position_y</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>source_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>source_description</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>detector_description</t>
+          <t>wavelength</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>pixel_size_x</t>
+          <t>wavelength_spread</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>pixel_size_y</t>
+          <t>wavelength_selection_method</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>sample_detector_distance</t>
+          <t>energy</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>rotation_angle</t>
+          <t>flux</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>beam_trap_type</t>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>q_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>q_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>number_of_guides</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>attenuator</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_aperature_diameter</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>sample_aperature_diameter</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>siwindow_to_main_distance</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>sample_ap_to_si_distance</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>beam_trap_position_x</t>
+          <t>sample_ap_to_main_distance</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>beam_trap_position_y</t>
+          <t>sample_ap_to_sample_distance</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
+          <t>source_ap_to_siwindow_distance</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>source_ap_to_sample_ap_distance</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
@@ -3013,144 +3308,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>source_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>source_description</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>wavelength</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>wavelength_spread</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>wavelength_selection_method</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>energy</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>flux</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>q_min</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>q_max</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>number_of_guides</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>attenuator</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>source_aperature_diameter</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>sample_aperature_diameter</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>siwindow_to_main_distance</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>sample_ap_to_si_distance</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>sample_ap_to_main_distance</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>sample_ap_to_sample_distance</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>source_ap_to_siwindow_distance</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>source_ap_to_sample_ap_distance</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3285,7 +3443,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3412,7 +3570,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3584,7 +3742,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3992,7 +4150,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4353,7 +4511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4442,7 +4600,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>value_cv_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>raw_value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4508,108 +4702,632 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>value_cv_id</t>
+<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>attribute</t>
+          <t>file_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>raw_value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dimensions_z</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>voxel_size</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>reconstruction_method</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>frames</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>super_resolution</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pixel_size_unbinned</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>timestamp</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stage_position_x</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>stage_position_y</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>stage_position_z</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>nominal_defocus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>dose_per_frame</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>beam_shift_x</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>beam_shift_y</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>ice_thickness_estimate</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>grid_square_id</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>hole_id</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>acquisition_group</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>defocus</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>astigmatism</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>origin_movie_id</t>
+        </is>
+      </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>defocus_u</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>defocus_v</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>astigmatism_angle</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>resolution_fit_limit</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ctf_quality_score</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>file_name</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:Q1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>wavenumber_min</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>wavenumber_max</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>spectral_resolution</t>
+        </is>
+      </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>number_of_scans</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>apodization_function</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>molecular_signatures</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>background_correction</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>acquisition_date</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>pixel_size</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>dimensions_x</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>dimensions_y</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>exposure_time</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>dose</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:U1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>excitation_wavelength</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>emission_wavelength</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>excitation_filter</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>emission_filter</t>
+        </is>
+      </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>fluorophore</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>channel_name</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>laser_power</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pinhole_size</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>quantum_yield</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>defocus</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>astigmatism</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>file_name</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>acquisition_date</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
           <t>pixel_size</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>dimensions_x</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>dimensions_y</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>exposure_time</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>dose</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
@@ -4620,567 +5338,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:M1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>dimensions_z</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>voxel_size</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>reconstruction_method</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AA1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>frames</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>super_resolution</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>pixel_size_unbinned</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>timestamp</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>stage_position_x</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>stage_position_y</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>stage_position_z</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>nominal_defocus</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>dose_per_frame</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>beam_shift_x</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>beam_shift_y</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ice_thickness_estimate</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>grid_square_id</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>hole_id</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>acquisition_group</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:R1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>origin_movie_id</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>defocus_u</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>defocus_v</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>astigmatism_angle</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>resolution_fit_limit</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>ctf_quality_score</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:Q1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>wavenumber_min</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>wavenumber_max</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>spectral_resolution</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>number_of_scans</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>apodization_function</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>molecular_signatures</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>background_correction</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:U1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>excitation_wavelength</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>emission_wavelength</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>excitation_filter</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>emission_filter</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>fluorophore</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>channel_name</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>laser_power</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>pinhole_size</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>quantum_yield</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>defocus</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>astigmatism</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>file_name</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>acquisition_date</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>pixel_size</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>dimensions_x</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>dimensions_y</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>exposure_time</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>dose</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5291,7 +5449,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5420,7 +5578,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5446,7 +5604,38 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>attribute</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>raw_value</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5497,38 +5686,43 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>value</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>attribute</t>
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sequences</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>modifications</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>raw_value</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>ligands</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5540,17 +5734,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>sequences</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>modifications</t>
+          <t>ph</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>components</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>ligands</t>
+          <t>additives</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5564,7 +5758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5576,17 +5770,17 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>ph</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>components</t>
+          <t>temperature</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>duration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>additives</t>
+          <t>atmosphere</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5600,43 +5794,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>temperature</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>duration</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>atmosphere</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5778,7 +5936,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5869,7 +6027,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6020,7 +6178,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6066,7 +6224,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6117,7 +6275,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6266,37 +6424,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet59.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>xbeam</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>ybeam</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6389,6 +6516,37 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>xbeam</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ybeam</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:AH1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -6569,7 +6727,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet61.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6610,7 +6768,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet62.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6657,7 +6815,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet63.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6718,7 +6876,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet64.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6769,7 +6927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet65.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6830,7 +6988,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet66.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6896,7 +7054,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet67.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6927,7 +7085,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet68.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -6968,32 +7126,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet69.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>study_id</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>experiment_id</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -7137,6 +7269,32 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>experiment_id</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>study_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>workflow_id</t>
         </is>
       </c>
@@ -7146,7 +7304,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet71.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7187,7 +7345,78 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet72.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>sample_id</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>role</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>construct_id</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>copy_number</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>sequence_coverage</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>chain_ids</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>modifications</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>observed_molecular_weight</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="C2:C1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"target,subunit,binding_partner,fusion_partner,chaperone,contaminant,standard"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7223,7 +7452,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet73.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7249,7 +7478,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet74.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7285,7 +7514,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet75.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7321,7 +7550,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet76.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7367,7 +7596,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet77.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7403,7 +7632,147 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet78.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:V1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>feature_type</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>secondary_structure</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>solvent_accessibility</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>backbone_flexibility</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>disorder_probability</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>conformational_state</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>structural_motif</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>domain_assignment</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>domain_id</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>protein_id</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>pdb_entry</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>chain_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>residue_range</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>confidence_score</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>evidence_type</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>evidence_code</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>source_database</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>annotation_method</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>publication_ids</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>title</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>description</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="4">
+    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"alpha_helix,beta_sheet,beta_strand,turn,coil,disordered_region,transmembrane_helix,signal_peptide,transit_peptide,domain,repeat,zinc_finger,zinc_binding,coiled_coil,motif,cavity,channel,pore,hinge,linker"</formula1>
+    </dataValidation>
+    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"helix,sheet,turn,coil,helix_310,helix_pi,bend,bridge"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"open,closed,intermediate,active,inactive,apo,holo,substrate_bound,product_bound,inhibitor_bound,partially_open,partially_closed,disordered"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7439,7 +7808,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet79.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet81.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -7480,147 +7849,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:V1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>feature_type</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>secondary_structure</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>solvent_accessibility</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>backbone_flexibility</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>disorder_probability</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>conformational_state</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>structural_motif</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>domain_assignment</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>domain_id</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>protein_id</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>pdb_entry</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>chain_id</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>residue_range</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>confidence_score</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>evidence_type</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>evidence_code</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>source_database</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>annotation_method</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>publication_ids</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>title</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="4">
-    <dataValidation sqref="A2:A1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"alpha_helix,beta_sheet,beta_strand,turn,coil,disordered_region,transmembrane_helix,signal_peptide,transit_peptide,domain,repeat,zinc_finger,zinc_binding,coiled_coil,motif,cavity,channel,pore,hinge,linker"</formula1>
-    </dataValidation>
-    <dataValidation sqref="B2:B1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"helix,sheet,turn,coil,helix_310,helix_pi,bend,bridge"</formula1>
-    </dataValidation>
-    <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"open,closed,intermediate,active,inactive,apo,holo,substrate_bound,product_bound,inhibitor_bound,partially_open,partially_closed,disordered"</formula1>
-    </dataValidation>
-    <dataValidation sqref="O2:O1048576" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"experimental,predicted,inferred,literature,author_statement,curator_inference"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet80.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet82.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
